--- a/analysis/econometrics_outputs/contdid/Graficos/contracts/dose/contdid_cosine_nearest_dose_att.xlsx
+++ b/analysis/econometrics_outputs/contdid/Graficos/contracts/dose/contdid_cosine_nearest_dose_att.xlsx
@@ -488,10 +488,10 @@
         <v>864.071932141947</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>433.89663390884</v>
+        <v>705.552734163777</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -510,10 +510,10 @@
         <v>843.333173287855</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>416.218619818264</v>
+        <v>680.339624832148</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -532,10 +532,10 @@
         <v>830.127872075815</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>405.032917018527</v>
+        <v>668.05363191389</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -554,10 +554,10 @@
         <v>747.802244354922</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>336.664312582304</v>
+        <v>590.324515821534</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -576,10 +576,10 @@
         <v>725.62522410201</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>316.571621560991</v>
+        <v>553.318121652954</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -598,10 +598,10 @@
         <v>695.841861101071</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>289.416814899977</v>
+        <v>511.811172119674</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -620,10 +620,10 @@
         <v>664.548936029925</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>261.453111290623</v>
+        <v>477.441656849668</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -642,10 +642,10 @@
         <v>645.342471662919</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>244.604038450764</v>
+        <v>455.995311845951</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -664,10 +664,10 @@
         <v>645.342471662919</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>244.604038450764</v>
+        <v>455.995311845951</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -686,10 +686,10 @@
         <v>628.509469083791</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>230.049193260337</v>
+        <v>437.226206492819</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -708,10 +708,10 @@
         <v>596.942373574644</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>219.143003843533</v>
+        <v>396.843098285986</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -730,10 +730,10 @@
         <v>588.176110548171</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>212.712442911654</v>
+        <v>379.87869785945</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -752,10 +752,10 @@
         <v>561.338922354575</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>193.366455136783</v>
+        <v>346.829237903712</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -774,10 +774,10 @@
         <v>546.751182607361</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>183.082063947275</v>
+        <v>330.436568157472</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -796,10 +796,10 @@
         <v>518.128476145856</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>163.429462647899</v>
+        <v>298.178253579287</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -818,10 +818,10 @@
         <v>511.533682927637</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>159.008479380818</v>
+        <v>290.726526054843</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -840,10 +840,10 @@
         <v>504.525584628222</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>154.357575339419</v>
+        <v>283.800594263251</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -862,10 +862,10 @@
         <v>443.064827357563</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>115.970285329312</v>
+        <v>215.947113244725</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -884,10 +884,10 @@
         <v>410.653011714632</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>97.8736335763211</v>
+        <v>168.643995944808</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
@@ -906,10 +906,10 @@
         <v>410.653011714632</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>97.8736335763211</v>
+        <v>168.643995944808</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
@@ -928,10 +928,10 @@
         <v>392.185432032617</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>88.4238840850553</v>
+        <v>169.478943714493</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
@@ -950,10 +950,10 @@
         <v>370.586678763219</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>69.1185725231831</v>
+        <v>171.197528448699</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
@@ -972,10 +972,10 @@
         <v>365.522825614677</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>61.5559361790453</v>
+        <v>170.684059995075</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -994,10 +994,10 @@
         <v>340.752354347046</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>31.339070704543</v>
+        <v>149.657423328539</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -1016,10 +1016,10 @@
         <v>330.432929668532</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>31.2211215612607</v>
+        <v>152.360004012304</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
@@ -1038,10 +1038,10 @@
         <v>324.087212829395</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>31.0864327101965</v>
+        <v>146.987748853855</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -1060,10 +1060,10 @@
         <v>286.091876611811</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>66.7697556555307</v>
+        <v>139.297849771314</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -1082,10 +1082,10 @@
         <v>273.69663586243</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>75.2443026719795</v>
+        <v>145.334392919583</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -1104,10 +1104,10 @@
         <v>269.793528225084</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>77.2057518695295</v>
+        <v>147.514258584016</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -1126,10 +1126,10 @@
         <v>265.963709347117</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>78.7238315540845</v>
+        <v>146.599753020804</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -1148,10 +1148,10 @@
         <v>261.229490665092</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>79.9511341754784</v>
+        <v>146.307072625725</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -1170,10 +1170,10 @@
         <v>252.535386032857</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>79.8007699256034</v>
+        <v>141.053854760124</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -1192,10 +1192,10 @@
         <v>238.380692363011</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>67.8325779869437</v>
+        <v>154.703467178376</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
@@ -1214,10 +1214,10 @@
         <v>235.88942849362</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>62.751420313017</v>
+        <v>154.339552459556</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
@@ -1236,10 +1236,10 @@
         <v>233.917201606565</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>57.4501765617367</v>
+        <v>153.619302202904</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -1258,10 +1258,10 @@
         <v>231.486375806997</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>48.4460633863085</v>
+        <v>145.491375574454</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -1280,10 +1280,10 @@
         <v>230.361049972514</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>42.7617030525367</v>
+        <v>139.971073339218</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
@@ -1302,10 +1302,10 @@
         <v>229.066554062855</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>34.0167374599592</v>
+        <v>134.418057045477</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
@@ -1324,10 +1324,10 @@
         <v>228.891818509866</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>32.5494054673752</v>
+        <v>132.821295418574</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
@@ -1346,10 +1346,10 @@
         <v>227.175884821544</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>12.3378896409838</v>
+        <v>126.281977591734</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
@@ -1368,10 +1368,10 @@
         <v>228.074920089399</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>37.36675698258</v>
+        <v>136.745043248251</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
@@ -1390,10 +1390,10 @@
         <v>228.356373165061</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>42.5101139772451</v>
+        <v>140.503437296613</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
@@ -1412,10 +1412,10 @@
         <v>229.174907215398</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>55.0879692178722</v>
+        <v>145.670808593729</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
@@ -1434,10 +1434,10 @@
         <v>229.659112157768</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>61.3790819844008</v>
+        <v>143.997719006208</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
@@ -1456,10 +1456,10 @@
         <v>230.543478320695</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>71.3974750964711</v>
+        <v>142.258402846371</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
@@ -1478,10 +1478,10 @@
         <v>236.562921781231</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>115.618352420877</v>
+        <v>147.076082012805</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
@@ -1500,10 +1500,10 @@
         <v>241.483025727816</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>137.942523308541</v>
+        <v>159.504318780275</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
@@ -1522,10 +1522,10 @@
         <v>250.890662145281</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>165.993349851149</v>
+        <v>156.980797067414</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
@@ -1544,10 +1544,10 @@
         <v>260.81650236279</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>184.263284554701</v>
+        <v>158.172995530308</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
@@ -1566,10 +1566,10 @@
         <v>266.629760457784</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>191.587391427293</v>
+        <v>162.658237208056</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
@@ -1588,10 +1588,10 @@
         <v>270.099788650237</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>195.058971595314</v>
+        <v>164.448918133764</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
@@ -1610,10 +1610,10 @@
         <v>270.099788650237</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>195.058971595314</v>
+        <v>164.448918133764</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
@@ -1632,10 +1632,10 @@
         <v>271.855216406311</v>
       </c>
       <c r="F58" s="1" t="n">
-        <v>196.591255244901</v>
+        <v>164.998887331423</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
@@ -1654,10 +1654,10 @@
         <v>275.989390525432</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>199.663663678312</v>
+        <v>166.233304416376</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
@@ -1676,10 +1676,10 @@
         <v>281.993018492507</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>202.935564820959</v>
+        <v>167.939115926075</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
@@ -1698,10 +1698,10 @@
         <v>284.351800661512</v>
       </c>
       <c r="F61" s="1" t="n">
-        <v>203.878401303391</v>
+        <v>167.950516135474</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
@@ -1720,10 +1720,10 @@
         <v>299.613894704985</v>
       </c>
       <c r="F62" s="1" t="n">
-        <v>206.124000242047</v>
+        <v>167.73047871853</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
@@ -1742,10 +1742,10 @@
         <v>305.117642933515</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>205.549609145421</v>
+        <v>168.867020030043</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
@@ -1764,10 +1764,10 @@
         <v>316.00790828548</v>
       </c>
       <c r="F64" s="1" t="n">
-        <v>201.670330259541</v>
+        <v>170.659755673446</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
@@ -1786,10 +1786,10 @@
         <v>320.640832800402</v>
       </c>
       <c r="F65" s="1" t="n">
-        <v>197.958979711953</v>
+        <v>170.139193614591</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
@@ -1808,10 +1808,10 @@
         <v>352.220487060808</v>
       </c>
       <c r="F66" s="1" t="n">
-        <v>174.050457787396</v>
+        <v>166.22525460005</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
@@ -1830,10 +1830,10 @@
         <v>372.183458494432</v>
       </c>
       <c r="F67" s="1" t="n">
-        <v>159.887052349285</v>
+        <v>169.842543888708</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
@@ -1852,10 +1852,10 @@
         <v>380.708530906097</v>
       </c>
       <c r="F68" s="1" t="n">
-        <v>152.077510105657</v>
+        <v>170.771782869316</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
@@ -1874,10 +1874,10 @@
         <v>405.130665599576</v>
       </c>
       <c r="F69" s="1" t="n">
-        <v>122.684900777972</v>
+        <v>158.980847311251</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
@@ -1896,10 +1896,10 @@
         <v>417.820921695967</v>
       </c>
       <c r="F70" s="1" t="n">
-        <v>105.747875248832</v>
+        <v>157.738286654435</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
@@ -1918,10 +1918,10 @@
         <v>431.16478679324</v>
       </c>
       <c r="F71" s="1" t="n">
-        <v>86.8309908030065</v>
+        <v>162.495374361163</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
@@ -1940,10 +1940,10 @@
         <v>441.315477342136</v>
       </c>
       <c r="F72" s="1" t="n">
-        <v>71.7264738143945</v>
+        <v>164.519982399461</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H72" s="1"/>
       <c r="I72" s="1"/>
@@ -1962,10 +1962,10 @@
         <v>453.372786224539</v>
       </c>
       <c r="F73" s="1" t="n">
-        <v>53.024140982019</v>
+        <v>161.515070419423</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H73" s="1"/>
       <c r="I73" s="1"/>
@@ -1984,10 +1984,10 @@
         <v>484.270033360475</v>
       </c>
       <c r="F74" s="1" t="n">
-        <v>38.5303810496418</v>
+        <v>149.220171570434</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
@@ -2006,10 +2006,10 @@
         <v>495.593173735025</v>
       </c>
       <c r="F75" s="1" t="n">
-        <v>54.1177386605737</v>
+        <v>155.389023559364</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
@@ -2028,10 +2028,10 @@
         <v>499.716365092194</v>
       </c>
       <c r="F76" s="1" t="n">
-        <v>60.45648307178</v>
+        <v>161.066249791922</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
@@ -2050,10 +2050,10 @@
         <v>504.126784486136</v>
       </c>
       <c r="F77" s="1" t="n">
-        <v>67.2916988951708</v>
+        <v>161.895212099112</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
@@ -2072,10 +2072,10 @@
         <v>513.29528446166</v>
       </c>
       <c r="F78" s="1" t="n">
-        <v>81.6786404815436</v>
+        <v>158.989807602528</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
@@ -2094,10 +2094,10 @@
         <v>529.901041255645</v>
       </c>
       <c r="F79" s="1" t="n">
-        <v>108.326476287136</v>
+        <v>168.760678857507</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
@@ -2116,10 +2116,10 @@
         <v>548.057353504863</v>
       </c>
       <c r="F80" s="1" t="n">
-        <v>138.297037943292</v>
+        <v>186.959924739517</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H80" s="1"/>
       <c r="I80" s="1"/>
@@ -2138,10 +2138,10 @@
         <v>574.911043575074</v>
       </c>
       <c r="F81" s="1" t="n">
-        <v>184.152492695969</v>
+        <v>204.638904862702</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H81" s="1"/>
       <c r="I81" s="1"/>
@@ -2160,10 +2160,10 @@
         <v>579.623066919844</v>
       </c>
       <c r="F82" s="1" t="n">
-        <v>192.382511036027</v>
+        <v>208.659563929474</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
@@ -2182,10 +2182,10 @@
         <v>604.474471050317</v>
       </c>
       <c r="F83" s="1" t="n">
-        <v>244.349441269368</v>
+        <v>230.125778288732</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
@@ -2204,10 +2204,10 @@
         <v>624.777856409033</v>
       </c>
       <c r="F84" s="1" t="n">
-        <v>274.038553933569</v>
+        <v>249.707013014936</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H84" s="1"/>
       <c r="I84" s="1"/>
@@ -2226,10 +2226,10 @@
         <v>633.60834395311</v>
       </c>
       <c r="F85" s="1" t="n">
-        <v>285.135171405722</v>
+        <v>252.303764311632</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H85" s="1"/>
       <c r="I85" s="1"/>
@@ -2248,10 +2248,10 @@
         <v>652.456713650343</v>
       </c>
       <c r="F86" s="1" t="n">
-        <v>308.251222476847</v>
+        <v>273.944065944426</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H86" s="1"/>
       <c r="I86" s="1"/>
@@ -2270,10 +2270,10 @@
         <v>653.477052529834</v>
       </c>
       <c r="F87" s="1" t="n">
-        <v>309.509876941998</v>
+        <v>275.636433412311</v>
       </c>
       <c r="G87" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H87" s="1"/>
       <c r="I87" s="1"/>
@@ -2292,10 +2292,10 @@
         <v>670.09328734866</v>
       </c>
       <c r="F88" s="1" t="n">
-        <v>330.028089858362</v>
+        <v>301.973570552578</v>
       </c>
       <c r="G88" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H88" s="1"/>
       <c r="I88" s="1"/>
@@ -2314,10 +2314,10 @@
         <v>684.508774640336</v>
       </c>
       <c r="F89" s="1" t="n">
-        <v>347.642183071003</v>
+        <v>317.482407452759</v>
       </c>
       <c r="G89" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
@@ -2336,10 +2336,10 @@
         <v>694.27274176387</v>
       </c>
       <c r="F90" s="1" t="n">
-        <v>359.149473142626</v>
+        <v>328.909594576163</v>
       </c>
       <c r="G90" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H90" s="1"/>
       <c r="I90" s="1"/>
@@ -2358,10 +2358,10 @@
         <v>698.928367928922</v>
       </c>
       <c r="F91" s="1" t="n">
-        <v>364.326186484468</v>
+        <v>334.316575293579</v>
       </c>
       <c r="G91" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H91" s="1"/>
       <c r="I91" s="1"/>
@@ -2380,10 +2380,10 @@
         <v>699.049569693532</v>
       </c>
       <c r="F92" s="1" t="n">
-        <v>364.45625532702</v>
+        <v>334.46331078495</v>
       </c>
       <c r="G92" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
@@ -2402,10 +2402,10 @@
         <v>708.526154759591</v>
       </c>
       <c r="F93" s="1" t="n">
-        <v>372.188860938317</v>
+        <v>333.572631973019</v>
       </c>
       <c r="G93" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H93" s="1"/>
       <c r="I93" s="1"/>
@@ -2424,10 +2424,10 @@
         <v>702.810416611393</v>
       </c>
       <c r="F94" s="1" t="n">
-        <v>351.369859528203</v>
+        <v>348.750401426068</v>
       </c>
       <c r="G94" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
@@ -2446,10 +2446,10 @@
         <v>542.964100354043</v>
       </c>
       <c r="F95" s="1" t="n">
-        <v>35.8455811778427</v>
+        <v>444.182802394115</v>
       </c>
       <c r="G95" s="1" t="n">
-        <v>33.4149136912311</v>
+        <v>2.71363915691627</v>
       </c>
       <c r="H95" s="1"/>
       <c r="I95" s="1"/>
